--- a/plants_data/hydrogenPipelineOnshore.xlsx
+++ b/plants_data/hydrogenPipelineOnshore.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17F6B48-DDBA-4D2E-A2B5-5530522B0927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823DEAD5-500B-4598-AF9F-C2037B90F2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="distances" sheetId="5" r:id="rId1"/>
@@ -427,19 +427,19 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="D2">
-        <v>186.8</v>
+        <v>187</v>
       </c>
       <c r="E2">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>287.5</v>
+        <v>288</v>
       </c>
       <c r="G2">
-        <v>112.2</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -447,22 +447,22 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>232.7</v>
+        <v>233</v>
       </c>
       <c r="E3">
-        <v>119.8</v>
+        <v>120</v>
       </c>
       <c r="F3">
-        <v>382.8</v>
+        <v>383</v>
       </c>
       <c r="G3">
-        <v>150.19999999999999</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -470,22 +470,22 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>186.8</v>
+        <v>187</v>
       </c>
       <c r="C4">
-        <v>232.7</v>
+        <v>233</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>200.3</v>
+        <v>200</v>
       </c>
       <c r="F4">
-        <v>244.4</v>
+        <v>244</v>
       </c>
       <c r="G4">
-        <v>82.9</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -493,22 +493,22 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="C5">
-        <v>119.8</v>
+        <v>120</v>
       </c>
       <c r="D5">
-        <v>200.3</v>
+        <v>200</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>275.10000000000002</v>
+        <v>275</v>
       </c>
       <c r="G5">
-        <v>131.1</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -516,22 +516,22 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>287.5</v>
+        <v>288</v>
       </c>
       <c r="C6">
-        <v>382.8</v>
+        <v>383</v>
       </c>
       <c r="D6">
-        <v>244.4</v>
+        <v>244</v>
       </c>
       <c r="E6">
-        <v>275.10000000000002</v>
+        <v>275</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>273.8</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -539,19 +539,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>112.2</v>
+        <v>112</v>
       </c>
       <c r="C7">
-        <v>150.19999999999999</v>
+        <v>150</v>
       </c>
       <c r="D7">
-        <v>82.9</v>
+        <v>83</v>
       </c>
       <c r="E7">
-        <v>131.1</v>
+        <v>131</v>
       </c>
       <c r="F7">
-        <v>273.8</v>
+        <v>274</v>
       </c>
       <c r="G7">
         <v>0</v>

--- a/plants_data/hydrogenPipelineOnshore.xlsx
+++ b/plants_data/hydrogenPipelineOnshore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823DEAD5-500B-4598-AF9F-C2037B90F2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3C8C57-0CDD-4E80-BBAA-99E97EDEE287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="distances" sheetId="5" r:id="rId1"/>

--- a/plants_data/hydrogenPipelineOnshore.xlsx
+++ b/plants_data/hydrogenPipelineOnshore.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3C8C57-0CDD-4E80-BBAA-99E97EDEE287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8706BB7E-AAC0-41D6-AC1A-D00FEE5A34B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="distances" sheetId="5" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="8">
   <si>
     <t>cluster</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>NL2</t>
+  </si>
+  <si>
+    <t>NL4</t>
   </si>
 </sst>
 </file>
@@ -393,10 +396,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4105D017-131C-4477-AA72-D63313CED0A5}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -416,10 +419,13 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -433,16 +439,19 @@
         <v>187</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>288</v>
       </c>
       <c r="G2">
+        <v>51</v>
+      </c>
+      <c r="H2">
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -456,16 +465,19 @@
         <v>233</v>
       </c>
       <c r="E3">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="F3">
         <v>383</v>
       </c>
       <c r="G3">
+        <v>149</v>
+      </c>
+      <c r="H3">
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -479,39 +491,45 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="F4">
         <v>244</v>
       </c>
       <c r="G4">
+        <v>185</v>
+      </c>
+      <c r="H4">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C5">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="D5">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="G5">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="H5">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -525,35 +543,67 @@
         <v>244</v>
       </c>
       <c r="E6">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
+        <v>242</v>
+      </c>
+      <c r="H6">
         <v>274</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>51</v>
+      </c>
+      <c r="C7">
+        <v>149</v>
+      </c>
+      <c r="D7">
+        <v>185</v>
+      </c>
+      <c r="E7">
+        <v>67</v>
+      </c>
+      <c r="F7">
+        <v>242</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>112</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>150</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>83</v>
       </c>
-      <c r="E7">
-        <v>131</v>
-      </c>
-      <c r="F7">
+      <c r="E8">
+        <v>144</v>
+      </c>
+      <c r="F8">
         <v>274</v>
       </c>
-      <c r="G7">
+      <c r="G8">
+        <v>126</v>
+      </c>
+      <c r="H8">
         <v>0</v>
       </c>
     </row>
@@ -564,7 +614,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BCD7A9-DCF0-4163-88EF-8C5CFFF77653}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -573,7 +623,7 @@
     <col min="28" max="42" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -595,8 +645,11 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -618,8 +671,11 @@
       <c r="G2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -641,8 +697,11 @@
       <c r="G3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -664,8 +723,11 @@
       <c r="G4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -687,8 +749,11 @@
       <c r="G5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -710,8 +775,11 @@
       <c r="G6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -731,6 +799,35 @@
         <v>1</v>
       </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
         <v>0</v>
       </c>
     </row>
@@ -741,7 +838,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31942815-BCF5-49B9-8BFE-C3A7059AA2B1}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -750,7 +847,7 @@
     <col min="28" max="42" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -772,8 +869,11 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -795,8 +895,11 @@
       <c r="G2">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -818,8 +921,11 @@
       <c r="G3">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -841,8 +947,11 @@
       <c r="G4">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -864,8 +973,11 @@
       <c r="G5">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -887,8 +999,11 @@
       <c r="G6">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -908,6 +1023,35 @@
         <v>1000000</v>
       </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1000000</v>
+      </c>
+      <c r="C8">
+        <v>1000000</v>
+      </c>
+      <c r="D8">
+        <v>1000000</v>
+      </c>
+      <c r="E8">
+        <v>1000000</v>
+      </c>
+      <c r="F8">
+        <v>1000000</v>
+      </c>
+      <c r="G8">
+        <v>1000000</v>
+      </c>
+      <c r="H8">
         <v>0</v>
       </c>
     </row>
